--- a/src/data/timeline.xlsx
+++ b/src/data/timeline.xlsx
@@ -1,46 +1,276 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lyanc\VScodeProgram\inteplast_home_page_tw\src\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84A4492-2FEB-4E54-9348-08631E50FE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="公司時間軸" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="72">
+  <si>
+    <t>年份</t>
+  </si>
+  <si>
+    <t>標題</t>
+  </si>
+  <si>
+    <t>標題英文</t>
+  </si>
+  <si>
+    <t>說明</t>
+  </si>
+  <si>
+    <t>說明英文</t>
+  </si>
+  <si>
+    <t>未來展望</t>
+  </si>
+  <si>
+    <t>1983</t>
+  </si>
+  <si>
+    <t>台塑塑膠加工組，於前鎮廠起步</t>
+  </si>
+  <si>
+    <t>Formosa Plastics processing group begins at Qianzhen</t>
+  </si>
+  <si>
+    <t>高雄前鎮廠開始生產購物袋，開啟袋品製造歷程。</t>
+  </si>
+  <si>
+    <t>The Kaohsiung Qianzhen plant began producing shopping bags, starting its bag manufacturing history.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1984</t>
+  </si>
+  <si>
+    <t>The Qianzhen plant began producing produce bags, gradually expanding the product line.</t>
+  </si>
+  <si>
+    <t>1989</t>
+  </si>
+  <si>
+    <t>新港廠整地擴建</t>
+  </si>
+  <si>
+    <t>建立後續聚乙烯薄膜與袋品生產基地。</t>
+  </si>
+  <si>
+    <t>Foundation laid for polyethylene film and bag production.</t>
+  </si>
+  <si>
+    <t>1991</t>
+  </si>
+  <si>
+    <t>新港廠正式投產</t>
+  </si>
+  <si>
+    <t>Xingang plant begins production</t>
+  </si>
+  <si>
+    <t>啟用全自動拌料輸送系統，生產購物袋與清潔袋等產品。</t>
+  </si>
+  <si>
+    <t>An automated mixing and conveying system was introduced for shopping and refuse bag production.</t>
+  </si>
+  <si>
+    <t>1998</t>
+  </si>
+  <si>
+    <t>引進附拉繩清潔袋設備</t>
+  </si>
+  <si>
+    <t>Draw-tape bag equipment introduced</t>
+  </si>
+  <si>
+    <t>由歐美引進新型設備，回應國內環保需求。</t>
+  </si>
+  <si>
+    <t>New equipment was introduced from Europe and the United States to meet domestic environmental needs.</t>
+  </si>
+  <si>
+    <t>1990s
+–2000s</t>
+  </si>
+  <si>
+    <t>跨海技術合作，建立長期默契</t>
+  </si>
+  <si>
+    <t>Cross-Pacific technical collaboration</t>
+  </si>
+  <si>
+    <t>隨著美國 INTEPLAST 擴建製造能力，新港廠技術人員曾赴美支援現場導入與技術交流。這段跨國協作，讓雙方在塑膠加工、設備運作與製造管理上累積共同經驗，也為後續更深度的合作建立基礎。</t>
+  </si>
+  <si>
+    <t>As INTEPLAST expanded its manufacturing capability in the United States, technical personnel from Xingang supported on-site implementation and knowledge exchange. The collaboration built shared experience in plastics processing, equipment operations, and manufacturing management.</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>高雄前鎮廠遷廠合併</t>
+  </si>
+  <si>
+    <t>Kaohsiung Qianzhen plant consolidated</t>
+  </si>
+  <si>
+    <t>整合市場袋生產，擴大新港生產配置。</t>
+  </si>
+  <si>
+    <t>Produce-bag production was consolidated into Xingang.</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>全球產品配置重整</t>
+  </si>
+  <si>
+    <t>Global production realignment</t>
+  </si>
+  <si>
+    <t>購物袋移往越南廠生產，新港聚焦清潔袋、附拉繩清潔袋及市場袋。</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>台塑塑膠加工組獨立成立臺灣營德股份有限公司，延續製造根基，並持續作為台塑相關企業的一員。</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>投入研發滑塊袋產品</t>
+  </si>
+  <si>
+    <t>Slider bag development begins</t>
+  </si>
+  <si>
+    <t>延伸密封包裝產品技術，投入滑塊袋產品的研發與製程能力建置。</t>
+  </si>
+  <si>
+    <t>Development began on slider bags, extending our resealable packaging capabilities and process expertise.</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>Medical IV overwrap developed</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>把製造能力，推向下一個可能</t>
+  </si>
+  <si>
+    <t>Advancing manufacturing for what comes next</t>
+  </si>
+  <si>
+    <t>We are advancing functional films, medical packaging, and sustainable products—bringing more agile technology and dependable quality to the market needs ahead.</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>越南營德公司成立</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>市場袋、清潔袋加入產品線</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前鎮廠開始生產市場袋、清潔袋，產品線逐步擴展。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>開發醫療點滴用外袋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因應醫療用袋需求增加，完成點滴用外袋開發。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台塑塑膠加工組改組，加入美國INTEPLAST GROUP，臺灣營德股份有限公司正式成立</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>越南營德公司生產清潔袋、市場袋、食品袋、八折袋、冰袋、Scale Sheet(Tare Sheet)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持續深化功能性薄膜、醫療包裝與永續產品，讓新港及越南基地以更靈活的技術與更穩定的品質，服務下一階段的市場需求。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Produce and can liner bags added to the product line</t>
+  </si>
+  <si>
+    <t>Xingang Plant expansion begins</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Formosa Plastics Processing Division joins INTEPLAST GROUP, establishing INTEPLAST TAIWAN</t>
+  </si>
+  <si>
+    <t>INTEPLAST VIETNAM established</t>
+  </si>
+  <si>
+    <t>In response to growing demand for medical packaging, developed IV overwrap bags.</t>
+  </si>
+  <si>
+    <t>INTEPLAST VIETNAM expanded its product portfolio to include can liners, produce bags, food storage bags, folded bags, ice bags, and Scale Sheets (Tare Sheets).</t>
+  </si>
+  <si>
+    <t>The Formosa Plastics Processing Division was established as INTEPLAST TAIWAN CORPORATION, building on its manufacturing heritage as part of the Formosa Plastics affiliated group.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shopping bag production moved to Vietnam, while Xingang focused on can liners, drawstring bags, and produce bags.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -64,14 +294,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,281 +637,301 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" customWidth="1"/>
-    <col min="4" max="4" width="54.83203125" customWidth="1"/>
-    <col min="5" max="5" width="60.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="92.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53" customWidth="1"/>
+    <col min="4" max="4" width="93.77734375" customWidth="1"/>
+    <col min="5" max="5" width="60.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>年份</v>
-      </c>
-      <c r="B1" t="str">
-        <v>標題</v>
-      </c>
-      <c r="C1" t="str">
-        <v>標題英文</v>
-      </c>
-      <c r="D1" t="str">
-        <v>說明</v>
-      </c>
-      <c r="E1" t="str">
-        <v>說明英文</v>
-      </c>
-      <c r="F1" t="str">
-        <v>未來展望</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1983</v>
-      </c>
-      <c r="B2" t="str">
-        <v>台塑塑膠加工組，於前鎮廠起步</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Formosa Plastics processing group begins at Qianzhen</v>
-      </c>
-      <c r="D2" t="str">
-        <v>高雄前鎮廠開始生產購物袋，開啟袋品製造歷程。</v>
-      </c>
-      <c r="E2" t="str">
-        <v>The Kaohsiung Qianzhen plant began producing shopping bags, starting its bag manufacturing history.</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>1984</v>
-      </c>
-      <c r="B3" t="str">
-        <v>市場袋加入產品線</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Produce bags join the product line</v>
-      </c>
-      <c r="D3" t="str">
-        <v>前鎮廠開始生產市場袋，產品線逐步擴展。</v>
-      </c>
-      <c r="E3" t="str">
-        <v>The Qianzhen plant began producing produce bags, gradually expanding the product line.</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>1989</v>
-      </c>
-      <c r="B4" t="str">
-        <v>新港廠整地擴建</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Xingang plant expansion</v>
-      </c>
-      <c r="D4" t="str">
-        <v>建立後續聚乙烯薄膜與袋品生產基地。</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Foundation laid for polyethylene film and bag production.</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>1991</v>
-      </c>
-      <c r="B5" t="str">
-        <v>新港廠正式投產</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Xingang plant begins production</v>
-      </c>
-      <c r="D5" t="str">
-        <v>啟用全自動拌料輸送系統，生產購物袋與清潔袋等產品。</v>
-      </c>
-      <c r="E5" t="str">
-        <v>An automated mixing and conveying system was introduced for shopping and refuse bag production.</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1998</v>
-      </c>
-      <c r="B6" t="str">
-        <v>引進附拉繩清潔袋設備</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Draw-tape bag equipment introduced</v>
-      </c>
-      <c r="D6" t="str">
-        <v>由歐美引進新型設備，回應國內環保需求。</v>
-      </c>
-      <c r="E6" t="str">
-        <v>New equipment was introduced from Europe and the United States to meet domestic environmental needs.</v>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1990s
-–2000s</v>
-      </c>
-      <c r="B7" t="str">
-        <v>跨海技術合作，建立長期默契</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Cross-Pacific technical collaboration</v>
-      </c>
-      <c r="D7" t="str">
-        <v>隨著美國 INTEPLAST 擴建製造能力，新港廠技術人員曾赴美支援現場導入與技術交流。這段跨國協作，讓雙方在塑膠加工、設備運作與製造管理上累積共同經驗，也為後續更深度的合作建立基礎。</v>
-      </c>
-      <c r="E7" t="str">
-        <v>As INTEPLAST expanded its manufacturing capability in the United States, technical personnel from Xingang supported on-site implementation and knowledge exchange. The collaboration built shared experience in plastics processing, equipment operations, and manufacturing management.</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2004</v>
-      </c>
-      <c r="B8" t="str">
-        <v>高雄前鎮廠遷廠合併</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Kaohsiung Qianzhen plant consolidated</v>
-      </c>
-      <c r="D8" t="str">
-        <v>整合市場袋生產，擴大新港生產配置。</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Produce-bag production was consolidated into Xingang.</v>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>2008</v>
-      </c>
-      <c r="B9" t="str">
-        <v>全球產品配置重整</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Global production realignment</v>
-      </c>
-      <c r="D9" t="str">
-        <v>購物袋移往越南廠生產，新港聚焦清潔袋、附拉繩清潔袋及市場袋。</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Shopping bags moved to Vietnam while Xingang focused on refuse, draw-tape and produce bags.</v>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>2014</v>
-      </c>
-      <c r="B10" t="str">
-        <v>塑膠加工組獨立，臺灣營德正式成立</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Processing group becomes INTEPLAST TAIWAN</v>
-      </c>
-      <c r="D10" t="str">
-        <v>台塑塑膠加工組獨立成立臺灣營德股份有限公司，延續製造根基，並持續作為台塑相關企業的一員。</v>
-      </c>
-      <c r="E10" t="str">
-        <v>The Formosa Plastics processing group became INTEPLAST TAIWAN CORPORATION, continuing its manufacturing foundation as part of the Formosa Plastics affiliated enterprise network.</v>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2017</v>
-      </c>
-      <c r="B11" t="str">
-        <v>投入研發滑塊袋產品</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Slider bag development begins</v>
-      </c>
-      <c r="D11" t="str">
-        <v>延伸密封包裝產品技術，投入滑塊袋產品的研發與製程能力建置。</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Development began on slider bags, extending our resealable packaging capabilities and process expertise.</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>2020</v>
-      </c>
-      <c r="B12" t="str">
-        <v>開發醫療用點滴外袋</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Medical IV overwrap developed</v>
-      </c>
-      <c r="D12" t="str">
-        <v>因應醫療用袋需求增加，完成點滴用外袋開發。</v>
-      </c>
-      <c r="E12" t="str">
-        <v>In response to growing medical demand, IV overwrap production was developed.</v>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2026</v>
-      </c>
-      <c r="B13" t="str">
-        <v>把製造能力，推向下一個可能</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Advancing manufacturing for what comes next</v>
-      </c>
-      <c r="D13" t="str">
-        <v>持續深化功能性薄膜、醫療包裝與永續產品，讓新港基地以更靈活的技術與更穩定的品質，服務下一階段的市場需求。</v>
-      </c>
-      <c r="E13" t="str">
-        <v>We are advancing functional films, medical packaging, and sustainable products—bringing more agile technology and dependable quality to the market needs ahead.</v>
-      </c>
-      <c r="F13" t="str">
-        <v>是</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>2015</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
+    <ignoredError sqref="A12:F12 A1:F2 A10 A5:F8 A3 E3:F3 A14:C14 A13 C13 F13 D10 E14:F14 A4:B4 D4:F4 F10 A9:D9 F9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>